--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_coquimbo_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_coquimbo_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:11</t>
+    <t xml:space="preserve">2026-09-29 14:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_coquimbo_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_coquimbo_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:07</t>
+    <t xml:space="preserve">2026-09-29 18:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -504,10 +504,10 @@
         <v>2.6</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>39.9</v>
+        <v>39.89</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>37.29</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="4">
@@ -521,7 +521,7 @@
         <v>28.26</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>29.96</v>
+        <v>29.95</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_coquimbo_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_coquimbo_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:38</t>
+    <t xml:space="preserve">2026-10-05 04:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -504,7 +504,7 @@
         <v>2.6</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>39.89</v>
+        <v>39.9</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>37.3</v>
@@ -518,10 +518,10 @@
         <v>-1.69</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>28.26</v>
+        <v>28.27</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>29.95</v>
+        <v>29.96</v>
       </c>
     </row>
   </sheetData>
